--- a/employee_surveys/032_marketing_campaign_management_employment_feedback_form--employee_surveys.xlsx
+++ b/employee_surveys/032_marketing_campaign_management_employment_feedback_form--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -593,7 +593,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>rating_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>process_evaluation</t>
+          <t>process_evaluation_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Process Evaluation</t>
+          <t>Process Evaluation 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>process_outcomes</t>
+          <t>process_outcomes_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Process Outcomes</t>
+          <t>Process Outcomes 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>campaign_process_goals</t>
+          <t>campaign_process_goals_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Campaign Process Goals</t>
+          <t>Campaign Process Goals 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1099,8 +1099,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'bob'}</t>
+          <t>bob</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Bob'}</t>
+          <t>Bob</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -1264,63 +1264,63 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>process_evaluation_choices</t>
+          <t>process_evaluation_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>process_evaluation_choices</t>
+          <t>process_evaluation_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>process_evaluation_choices</t>
+          <t>process_evaluation_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1366,12 +1366,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
